--- a/Files/rajdhani-day-penal-chart.xlsx
+++ b/Files/rajdhani-day-penal-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$459</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$460</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2399,6 +2399,9 @@
   </x:si>
   <x:si>
     <x:t>24/08/2026 to 29/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/08/2026 to 05/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -2854,7 +2857,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V459"/>
+  <x:dimension ref="A1:V460"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -34028,40 +34031,40 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="K459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="L459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="M459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="O459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="P459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="Q459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="R459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="S459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="T459" s="3" t="s">
         <x:v>41</x:v>
@@ -34073,8 +34076,76 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="460" spans="1:22">
+      <x:c r="A460" s="3" t="s">
+        <x:v>794</x:v>
+      </x:c>
+      <x:c r="B460" s="3" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C460" s="3" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D460" s="3" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V460" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V459"/>
+  <x:autoFilter ref="A1:V460"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -34097,39 +34168,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>794</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>795</x:v>
+        <x:v>796</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>796</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>797</x:v>
+        <x:v>798</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>798</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>799</x:v>
+        <x:v>800</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>800</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>458</x:v>
+        <x:v>459</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>801</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -34137,10 +34208,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>802</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>793</x:v>
+        <x:v>794</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
